--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.52002975620094</v>
+        <v>11.45950483538265</v>
       </c>
       <c r="D2" t="n">
-        <v>70.32517788674986</v>
+        <v>11.42784140659685</v>
       </c>
       <c r="E2" t="n">
-        <v>22.25919647525787</v>
+        <v>3.617119427229404</v>
       </c>
       <c r="F2" t="n">
-        <v>15.61527366585923</v>
+        <v>2.537481970702125</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.73180932198858</v>
+        <v>4.668919014823144</v>
       </c>
       <c r="D3" t="n">
-        <v>52.49019490939943</v>
+        <v>8.529656672777408</v>
       </c>
       <c r="E3" t="n">
-        <v>22.25919647525787</v>
+        <v>3.617119427229404</v>
       </c>
       <c r="F3" t="n">
-        <v>15.61527366585923</v>
+        <v>2.537481970702125</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.874770021257731</v>
+        <v>1.442150128454381</v>
       </c>
       <c r="D4" t="n">
-        <v>26.51961717090827</v>
+        <v>4.309437790272595</v>
       </c>
       <c r="E4" t="n">
-        <v>22.25919647525787</v>
+        <v>3.617119427229404</v>
       </c>
       <c r="F4" t="n">
-        <v>15.61527366585923</v>
+        <v>2.537481970702125</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.55649212185116</v>
+        <v>5.615429969800815</v>
       </c>
       <c r="D5" t="n">
-        <v>47.2347905117076</v>
+        <v>7.675653458152485</v>
       </c>
       <c r="E5" t="n">
-        <v>22.25919647525787</v>
+        <v>3.617119427229404</v>
       </c>
       <c r="F5" t="n">
-        <v>15.61527366585923</v>
+        <v>2.537481970702125</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
